--- a/data/jaarrooster.xlsx
+++ b/data/jaarrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogonderwijs-my.sharepoint.com/personal/j_jacobs_arentheemcollege_nl/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="487" documentId="8_{92E86D80-DAF2-4552-B77D-B828FA18C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D40FBD22-FD1E-4712-96ED-6E6DC9967355}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="8_{92E86D80-DAF2-4552-B77D-B828FA18C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEB2E09F-9628-4177-A61D-79FF70B5052A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{263560B9-378B-48CE-A165-97368AFE49A3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="104">
   <si>
     <t>Dag</t>
   </si>
@@ -676,6 +676,12 @@
   </si>
   <si>
     <t>Bijzonderheden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2.4 </t>
+  </si>
+  <si>
+    <t>Herhalen 2.1 t/m 2.4</t>
   </si>
 </sst>
 </file>
@@ -3039,8 +3045,12 @@
         <v>46328</v>
       </c>
       <c r="C22" s="62"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="116"/>
+      <c r="D22" s="115" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="115" t="s">
+        <v>102</v>
+      </c>
       <c r="F22" s="116"/>
       <c r="G22" s="116"/>
       <c r="H22" s="99"/>
@@ -3048,10 +3058,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="53"/>
-      <c r="B23" s="54"/>
+      <c r="B23" s="54">
+        <v>46330</v>
+      </c>
       <c r="C23" s="47"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="15"/>
+      <c r="D23" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="76" t="s">
+        <v>102</v>
+      </c>
       <c r="F23" s="21" t="s">
         <v>86</v>
       </c>
@@ -3061,10 +3077,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="60"/>
-      <c r="B24" s="61"/>
+      <c r="B24" s="61">
+        <v>46331</v>
+      </c>
       <c r="C24" s="49"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="71"/>
+      <c r="D24" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="77" t="s">
+        <v>103</v>
+      </c>
       <c r="F24" s="71"/>
       <c r="G24" s="71"/>
       <c r="H24" s="65"/>
